--- a/data/trans_orig/P64E-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P64E-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de personas que trabajan bajo su responsabilidad en 2007</t>
+          <t>Población según el número de personas que trabajan bajo su responsabilidad en 2007 (tasa de respuesta: 98,58%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11230</t>
+          <t>10960</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>864</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6878</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14867</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11477</t>
+          <t>13747</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5050</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13017</t>
+          <t>13462</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15737</t>
+          <t>14751</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16561</t>
+          <t>15743</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33011</t>
+          <t>33193</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57178</t>
+          <t>58686</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10491</t>
+          <t>10597</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27530</t>
+          <t>27786</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47769</t>
+          <t>49464</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78659</t>
+          <t>78735</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,81%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>303354</t>
+          <t>302579</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>330530</t>
+          <t>331916</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>119278</t>
+          <t>118945</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>136945</t>
+          <t>137510</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>429362</t>
+          <t>427253</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>463598</t>
+          <t>462271</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>86,94%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14122</t>
+          <t>14587</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,49 +1430,49 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1939</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6797</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
           <t>2,56%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1939</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6778</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>7</t>
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16562</t>
+          <t>15043</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8182</t>
+          <t>7470</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25194</t>
+          <t>24709</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>932</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10166</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28364</t>
+          <t>28159</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>23817</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>8476</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9406</t>
+          <t>10561</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27557</t>
+          <t>29703</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67004</t>
+          <t>66583</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>103576</t>
+          <t>100941</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11932</t>
+          <t>11772</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28791</t>
+          <t>28493</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83414</t>
+          <t>84208</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122639</t>
+          <t>124177</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>411216</t>
+          <t>413644</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>451464</t>
+          <t>455129</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>227004</t>
+          <t>226990</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>246631</t>
+          <t>246950</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>649090</t>
+          <t>649452</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>696262</t>
+          <t>694190</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,85%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21476</t>
+          <t>21728</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>970</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7807</t>
+          <t>7835</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>8191</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25787</t>
+          <t>24866</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15057</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>977</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9639</t>
+          <t>9704</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6642</t>
+          <t>6822</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20516</t>
+          <t>20510</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>5793</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19205</t>
+          <t>18970</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>799</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6733</t>
+          <t>7365</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8165</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22058</t>
+          <t>22507</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63178</t>
+          <t>63274</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>96046</t>
+          <t>96305</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9938</t>
+          <t>9968</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26343</t>
+          <t>25837</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79286</t>
+          <t>79249</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>115002</t>
+          <t>115228</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>275873</t>
+          <t>275629</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>311712</t>
+          <t>312933</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>175650</t>
+          <t>177428</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>195002</t>
+          <t>195165</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>460248</t>
+          <t>458889</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>500156</t>
+          <t>502172</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3484</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15661</t>
+          <t>15194</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7580</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17162</t>
+          <t>17854</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3552</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14802</t>
+          <t>14807</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>3024</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16522</t>
+          <t>15826</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8736</t>
+          <t>9513</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>25511</t>
+          <t>27644</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>9564</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26238</t>
+          <t>26128</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>933</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8371</t>
+          <t>8914</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11671</t>
+          <t>11954</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29208</t>
+          <t>29653</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>62459</t>
+          <t>60899</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>91466</t>
+          <t>93037</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17747</t>
+          <t>17525</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37370</t>
+          <t>37867</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>85699</t>
+          <t>85197</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>123960</t>
+          <t>122163</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>420608</t>
+          <t>418844</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>455507</t>
+          <t>456082</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>336201</t>
+          <t>333947</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>359021</t>
+          <t>358903</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>764679</t>
+          <t>762387</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>807347</t>
+          <t>807243</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,41%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20839</t>
+          <t>21475</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>43376</t>
+          <t>44181</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t>4769</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17195</t>
+          <t>16554</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>28684</t>
+          <t>27229</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>54770</t>
+          <t>54350</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24830</t>
+          <t>24859</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49246</t>
+          <t>49936</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,44 +3594,44 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>16457</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>9543</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>26524</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
           <t>2,61%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>16457</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>10008</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>27092</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>48</t>
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>39237</t>
+          <t>38716</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>69218</t>
+          <t>68742</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>38788</t>
+          <t>38088</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>65172</t>
+          <t>66490</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>17832</t>
+          <t>18738</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>46727</t>
+          <t>46098</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>78312</t>
+          <t>75946</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>254559</t>
+          <t>254550</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>314118</t>
+          <t>313236</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>62984</t>
+          <t>63185</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>96204</t>
+          <t>99190</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>330000</t>
+          <t>327103</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>399845</t>
+          <t>400040</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1449227</t>
+          <t>1448314</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1517880</t>
+          <t>1521671</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>881108</t>
+          <t>879254</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>922277</t>
+          <t>922111</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2345920</t>
+          <t>2346319</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2431779</t>
+          <t>2427134</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,62%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de personas que trabajan bajo su responsabilidad en 2012</t>
+          <t>Población según el número de personas que trabajan bajo su responsabilidad en 2012 (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>10358</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4740</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>862</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11008</t>
+          <t>10622</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>9875</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5038</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11806</t>
+          <t>12207</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6851</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21719</t>
+          <t>22501</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7752</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22797</t>
+          <t>24774</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26863</t>
+          <t>26739</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48439</t>
+          <t>49173</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18817</t>
+          <t>18814</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36845</t>
+          <t>35616</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62167</t>
+          <t>62616</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>200860</t>
+          <t>200863</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>227812</t>
+          <t>227316</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>139022</t>
+          <t>140520</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>154088</t>
+          <t>154813</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>348238</t>
+          <t>345893</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>378236</t>
+          <t>377164</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,06%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14810</t>
+          <t>15726</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16707</t>
+          <t>16845</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>959</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>9699</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>6485</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12075</t>
+          <t>12808</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>5831</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20566</t>
+          <t>19925</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>8513</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8472</t>
+          <t>8433</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23155</t>
+          <t>24146</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59252</t>
+          <t>58208</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91177</t>
+          <t>92156</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20235</t>
+          <t>21943</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46001</t>
+          <t>47189</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87009</t>
+          <t>86847</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>128025</t>
+          <t>129437</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,14%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>291490</t>
+          <t>290951</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>328203</t>
+          <t>326854</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>217675</t>
+          <t>216461</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>243460</t>
+          <t>243557</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>517886</t>
+          <t>517878</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>563567</t>
+          <t>563766</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,36%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18652</t>
+          <t>18282</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22465</t>
+          <t>21662</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13842</t>
+          <t>14681</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>962</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8225</t>
+          <t>8556</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17394</t>
+          <t>18737</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10547</t>
+          <t>11074</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5985,7 +5985,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10038</t>
+          <t>10024</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16320</t>
+          <t>15203</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48286</t>
+          <t>48204</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>77427</t>
+          <t>78306</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>13846</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31052</t>
+          <t>32641</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>67899</t>
+          <t>67108</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101522</t>
+          <t>102669</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224403</t>
+          <t>223436</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>256941</t>
+          <t>256973</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>173699</t>
+          <t>172996</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>194449</t>
+          <t>194583</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>407238</t>
+          <t>405647</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>445633</t>
+          <t>445216</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,95%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21593</t>
+          <t>22055</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>4861</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6573</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23495</t>
+          <t>23182</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19832</t>
+          <t>18208</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11404</t>
+          <t>12473</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>24243</t>
+          <t>25179</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4944</t>
+          <t>4803</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18642</t>
+          <t>20129</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>959</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9239</t>
+          <t>8597</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23909</t>
+          <t>23048</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>73757</t>
+          <t>73963</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>107381</t>
+          <t>107687</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15320</t>
+          <t>15360</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34223</t>
+          <t>36227</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>95084</t>
+          <t>94390</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>135225</t>
+          <t>133497</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>274717</t>
+          <t>273881</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>314117</t>
+          <t>313517</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>255489</t>
+          <t>254654</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>278187</t>
+          <t>278032</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>539024</t>
+          <t>540511</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>585789</t>
+          <t>585246</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,59%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>19349</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46986</t>
+          <t>43996</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10817</t>
+          <t>12073</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>24088</t>
+          <t>22776</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>52410</t>
+          <t>49848</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15597</t>
+          <t>16346</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>36369</t>
+          <t>37129</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4992</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>18923</t>
+          <t>18501</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>23455</t>
+          <t>23643</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>48130</t>
+          <t>48451</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>28363</t>
+          <t>27106</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>55589</t>
+          <t>53869</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5838</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>20025</t>
+          <t>20283</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,47 +7379,47 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>49778</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>37638</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>67110</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
           <t>2,11%</t>
         </is>
       </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>49778</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>36198</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>65272</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>232420</t>
+          <t>230358</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>290564</t>
+          <t>290557</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,7 +7457,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>70613</t>
+          <t>72429</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>109278</t>
+          <t>113347</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>314648</t>
+          <t>315856</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>388443</t>
+          <t>386487</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1025928</t>
+          <t>1027003</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1092137</t>
+          <t>1093307</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>808598</t>
+          <t>808509</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>854273</t>
+          <t>850736</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1851510</t>
+          <t>1855862</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1933507</t>
+          <t>1935645</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,9%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de personas que trabajan bajo su responsabilidad en 2016</t>
+          <t>Población según el número de personas que trabajan bajo su responsabilidad en 2016 (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8052,62 +8052,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1835</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5293</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1021</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5136</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>953</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>7810</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6630</t>
+          <t>5770</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10604</t>
+          <t>10542</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11187</t>
+          <t>10470</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>810</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7280</t>
+          <t>7532</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3631</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14383</t>
+          <t>14414</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16240</t>
+          <t>16554</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35221</t>
+          <t>34631</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>3558</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15634</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23791</t>
+          <t>23124</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44982</t>
+          <t>45135</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>197244</t>
+          <t>196156</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>218070</t>
+          <t>217291</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>145551</t>
+          <t>146147</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>159769</t>
+          <t>160259</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>349592</t>
+          <t>349349</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>373906</t>
+          <t>373948</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,31%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16318</t>
+          <t>15431</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12650</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6797</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22404</t>
+          <t>22350</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10747</t>
+          <t>10458</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11583</t>
+          <t>11606</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7127</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22445</t>
+          <t>22200</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8676</t>
+          <t>8823</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25395</t>
+          <t>26276</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27063</t>
+          <t>25840</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50831</t>
+          <t>50187</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10054</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27348</t>
+          <t>26254</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40614</t>
+          <t>41430</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71365</t>
+          <t>70890</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>332566</t>
+          <t>331891</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>362802</t>
+          <t>362809</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>234679</t>
+          <t>236218</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>256007</t>
+          <t>255719</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>577200</t>
+          <t>577530</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>613023</t>
+          <t>612027</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,59%</t>
         </is>
       </c>
     </row>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8595</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6819</t>
+          <t>6737</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12068</t>
+          <t>11372</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13275</t>
+          <t>13522</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4685</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15981</t>
+          <t>14390</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>3172</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15581</t>
+          <t>16445</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5373</t>
+          <t>5974</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>19920</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44110</t>
+          <t>44875</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74190</t>
+          <t>73725</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16135</t>
+          <t>16625</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36238</t>
+          <t>36484</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>67187</t>
+          <t>66600</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101696</t>
+          <t>103890</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264226</t>
+          <t>265356</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>297822</t>
+          <t>297571</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>227242</t>
+          <t>225778</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>248043</t>
+          <t>247555</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>499203</t>
+          <t>500232</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>540082</t>
+          <t>539578</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,04%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2491</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13655</t>
+          <t>14244</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3631</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16032</t>
+          <t>15690</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>17013</t>
+          <t>17661</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>10057</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27900</t>
+          <t>27520</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18227</t>
+          <t>17998</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16688</t>
+          <t>17113</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>38789</t>
+          <t>36785</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>41618</t>
+          <t>42546</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>69363</t>
+          <t>70705</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15607</t>
+          <t>14873</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35589</t>
+          <t>35475</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>63862</t>
+          <t>62608</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>96016</t>
+          <t>95905</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>297046</t>
+          <t>297280</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>328637</t>
+          <t>329193</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>272992</t>
+          <t>273010</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>296199</t>
+          <t>296519</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>579490</t>
+          <t>579521</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>617429</t>
+          <t>621395</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>86,32%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10594</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>28034</t>
+          <t>28174</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>2846</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15078</t>
+          <t>14310</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>16815</t>
+          <t>16509</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>37130</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11025</t>
+          <t>10954</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31159</t>
+          <t>28978</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11583</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14811</t>
+          <t>16582</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>36420</t>
+          <t>37969</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31646</t>
+          <t>30380</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>60821</t>
+          <t>58455</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10253</t>
+          <t>9850</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>27037</t>
+          <t>27766</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>45823</t>
+          <t>45425</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>80192</t>
+          <t>79346</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>152560</t>
+          <t>151607</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>205253</t>
+          <t>205467</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>57999</t>
+          <t>57211</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>92702</t>
+          <t>93539</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>223226</t>
+          <t>221237</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>281094</t>
+          <t>283914</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1121284</t>
+          <t>1117800</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1183372</t>
+          <t>1179155</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>906606</t>
+          <t>903536</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>945100</t>
+          <t>944572</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2039356</t>
+          <t>2039275</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2110433</t>
+          <t>2111529</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,55%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de personas que trabajan bajo su responsabilidad en 2023</t>
+          <t>Población según el número de personas que trabajan bajo su responsabilidad en 2023 (tasa de respuesta: 99,17%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>7478</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11694,62 +11694,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2181</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1199</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6889</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2181</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>8868</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8922</t>
+          <t>8431</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9606</t>
+          <t>10092</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21719</t>
+          <t>22990</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9343</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6779</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25447</t>
+          <t>27660</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25587</t>
+          <t>25484</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52068</t>
+          <t>52071</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,7 +12013,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7575</t>
+          <t>8321</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17608</t>
+          <t>17841</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36815</t>
+          <t>36822</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65763</t>
+          <t>64271</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>263179</t>
+          <t>262650</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>294828</t>
+          <t>294991</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>233916</t>
+          <t>233759</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>246020</t>
+          <t>245847</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>504837</t>
+          <t>503966</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>536998</t>
+          <t>536859</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,87%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26827</t>
+          <t>25959</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>969</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7511</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>7570</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28104</t>
+          <t>27837</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14038</t>
+          <t>13409</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>562221</t>
+          <t>539719</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,47 +12469,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>67,19%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>7055</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3693</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>13367</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>1,75%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>69,99%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>7055</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>3623</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>12614</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20551</t>
+          <t>20594</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>764653</t>
+          <t>724394</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>60,08%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9462</t>
+          <t>11663</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48107</t>
+          <t>46840</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2505</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9212</t>
+          <t>9672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14947</t>
+          <t>15681</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>49139</t>
+          <t>50639</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21399</t>
+          <t>21126</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83680</t>
+          <t>82701</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23257</t>
+          <t>22967</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40604</t>
+          <t>40622</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39562</t>
+          <t>41928</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>110962</t>
+          <t>112276</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>198417</t>
+          <t>212818</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>655815</t>
+          <t>657186</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>345098</t>
+          <t>345829</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>366359</t>
+          <t>367125</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>381779</t>
+          <t>407914</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1022085</t>
+          <t>1019210</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,54%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5534</t>
+          <t>6036</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21032</t>
+          <t>22085</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13063,7 +13063,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13078,7 +13078,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23897</t>
+          <t>24181</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>3098</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17428</t>
+          <t>17130</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>887</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>6958</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19379</t>
+          <t>19868</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21435</t>
+          <t>20647</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13269,7 +13269,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10168</t>
+          <t>9673</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8974</t>
+          <t>9558</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25901</t>
+          <t>26639</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30339</t>
+          <t>30004</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55819</t>
+          <t>55782</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11170</t>
+          <t>10314</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25396</t>
+          <t>24922</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45433</t>
+          <t>45281</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75352</t>
+          <t>76528</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,38%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259619</t>
+          <t>261356</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>294726</t>
+          <t>294825</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>284233</t>
+          <t>284477</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>302540</t>
+          <t>302961</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>551783</t>
+          <t>549840</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>592982</t>
+          <t>592354</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,12%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6838</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20389</t>
+          <t>20510</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9812</t>
+          <t>9265</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9580</t>
+          <t>9560</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25840</t>
+          <t>25592</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13795,7 +13795,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>2082</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11123</t>
+          <t>11610</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>1849</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9665</t>
+          <t>9076</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5613</t>
+          <t>5342</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>17639</t>
+          <t>17510</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>5132</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16462</t>
+          <t>16686</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,82 +13946,82 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>7045</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>3399</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>13195</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>16513</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>9915</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>24945</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
           <t>1,04%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>7045</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>3210</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>12446</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>16513</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>10396</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>25231</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34934</t>
+          <t>34234</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>59909</t>
+          <t>60804</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15032</t>
+          <t>16719</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38662</t>
+          <t>39644</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>55870</t>
+          <t>55448</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>91541</t>
+          <t>93440</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>379128</t>
+          <t>379996</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>409470</t>
+          <t>410094</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>423134</t>
+          <t>423379</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>454883</t>
+          <t>453866</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>811480</t>
+          <t>810918</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>859318</t>
+          <t>860414</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,61%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>24085</t>
+          <t>26135</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>55854</t>
+          <t>56873</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4968</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15002</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>35185</t>
+          <t>34726</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>67647</t>
+          <t>65618</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>31173</t>
+          <t>29133</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>748011</t>
+          <t>841803</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10298</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>23908</t>
+          <t>24807</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>44383</t>
+          <t>44420</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>994855</t>
+          <t>1046500</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14590,7 +14590,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>30,61%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>38728</t>
+          <t>37895</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>79881</t>
+          <t>81067</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>13638</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>28237</t>
+          <t>28578</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>56178</t>
+          <t>56775</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>101568</t>
+          <t>99179</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>121366</t>
+          <t>115859</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>219547</t>
+          <t>215602</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>71991</t>
+          <t>71042</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>106305</t>
+          <t>104656</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>205915</t>
+          <t>210249</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>308064</t>
+          <t>310194</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>994389</t>
+          <t>923314</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1617496</t>
+          <t>1620453</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1306396</t>
+          <t>1307397</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1353161</t>
+          <t>1351317</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2125754</t>
+          <t>2062109</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2959916</t>
+          <t>2959472</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,58%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P64E-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P64E-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10960</t>
+          <t>10841</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,77 +753,77 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2763</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>875</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7546</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,97%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>7711</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>3652</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>15298</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>2,88%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2763</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>864</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7355</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,85%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>7711</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>3651</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>15697</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13747</t>
+          <t>11424</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13462</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3873</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14751</t>
+          <t>15674</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4955</t>
+          <t>6154</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15743</t>
+          <t>16833</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33193</t>
+          <t>33126</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58686</t>
+          <t>58082</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10597</t>
+          <t>10633</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27786</t>
+          <t>27841</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49464</t>
+          <t>48269</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78735</t>
+          <t>79454</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,94%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>302579</t>
+          <t>301048</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>331916</t>
+          <t>330921</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>118945</t>
+          <t>118476</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>137510</t>
+          <t>137429</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>427253</t>
+          <t>427192</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>462271</t>
+          <t>461722</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,84%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14587</t>
+          <t>14300</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6797</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3548</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15043</t>
+          <t>16369</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7470</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24709</t>
+          <t>23662</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>945</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8993</t>
+          <t>8597</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>10624</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28159</t>
+          <t>29029</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8314</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23817</t>
+          <t>24244</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8476</t>
+          <t>8414</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10561</t>
+          <t>10528</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>29703</t>
+          <t>28658</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66583</t>
+          <t>67260</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100941</t>
+          <t>100665</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11772</t>
+          <t>11472</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28493</t>
+          <t>29040</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84208</t>
+          <t>83871</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>124177</t>
+          <t>122745</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>413644</t>
+          <t>412658</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>455129</t>
+          <t>452998</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>226990</t>
+          <t>227903</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>246950</t>
+          <t>247124</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>649452</t>
+          <t>648473</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>694190</t>
+          <t>693256</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,73%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21728</t>
+          <t>20740</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>959</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7835</t>
+          <t>7862</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8191</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24866</t>
+          <t>24157</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14896</t>
+          <t>14866</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>974</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9704</t>
+          <t>8874</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6822</t>
+          <t>6019</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20510</t>
+          <t>19232</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5793</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18970</t>
+          <t>19706</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>771</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7365</t>
+          <t>7653</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>8238</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22507</t>
+          <t>23920</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63274</t>
+          <t>64133</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>96305</t>
+          <t>94761</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9968</t>
+          <t>10492</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25837</t>
+          <t>25584</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79249</t>
+          <t>77188</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>115228</t>
+          <t>114071</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>275629</t>
+          <t>276843</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>312933</t>
+          <t>311837</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>177428</t>
+          <t>176320</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>195165</t>
+          <t>194758</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>458889</t>
+          <t>458611</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>502172</t>
+          <t>501755</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,11%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15194</t>
+          <t>15464</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>7178</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17854</t>
+          <t>18641</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3424</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14807</t>
+          <t>15849</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3024</t>
+          <t>2991</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>15826</t>
+          <t>16210</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9513</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>27644</t>
+          <t>27132</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9564</t>
+          <t>10055</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26128</t>
+          <t>26585</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>932</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8914</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11954</t>
+          <t>11668</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29653</t>
+          <t>29110</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>60899</t>
+          <t>61552</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>93037</t>
+          <t>92071</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17525</t>
+          <t>17070</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37867</t>
+          <t>37266</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>85197</t>
+          <t>84265</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>122163</t>
+          <t>121242</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>418844</t>
+          <t>420011</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>456082</t>
+          <t>456376</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>333947</t>
+          <t>334208</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>358903</t>
+          <t>358973</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>762387</t>
+          <t>764062</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>807243</t>
+          <t>809043</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,6%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21475</t>
+          <t>20439</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>44181</t>
+          <t>43583</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4769</t>
+          <t>4858</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16554</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27229</t>
+          <t>29413</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>54350</t>
+          <t>56346</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24859</t>
+          <t>25610</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49936</t>
+          <t>50431</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,82 +3589,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>16457</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>9577</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>28658</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>52097</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>38206</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>68542</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>16457</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>9543</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>26524</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>52097</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>38716</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>68742</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>38088</t>
+          <t>38231</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>66490</t>
+          <t>67392</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18738</t>
+          <t>16806</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>46098</t>
+          <t>46875</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>75946</t>
+          <t>77072</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>254550</t>
+          <t>252096</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>313236</t>
+          <t>313693</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>63185</t>
+          <t>63985</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>99190</t>
+          <t>98230</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>327103</t>
+          <t>326125</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>400040</t>
+          <t>395612</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1448314</t>
+          <t>1449391</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1521671</t>
+          <t>1518683</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>879254</t>
+          <t>879880</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>922111</t>
+          <t>922157</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2346319</t>
+          <t>2348372</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2427134</t>
+          <t>2429141</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,69%</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10358</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>923</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10622</t>
+          <t>11632</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9875</t>
+          <t>8991</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5038</t>
+          <t>4972</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12207</t>
+          <t>11481</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>7091</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>21875</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>7621</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24774</t>
+          <t>22730</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26739</t>
+          <t>26580</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49173</t>
+          <t>48850</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5557</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18814</t>
+          <t>19298</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35616</t>
+          <t>37081</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62616</t>
+          <t>64063</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>200863</t>
+          <t>200759</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>227316</t>
+          <t>227660</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>140520</t>
+          <t>139842</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>154813</t>
+          <t>153911</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>345893</t>
+          <t>344402</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>377164</t>
+          <t>376019</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,79%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15726</t>
+          <t>15045</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16845</t>
+          <t>16762</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>948</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9699</t>
+          <t>9420</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6485</t>
+          <t>6579</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2752</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12808</t>
+          <t>13734</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19925</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8513</t>
+          <t>8532</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>8465</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>24146</t>
+          <t>23814</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58208</t>
+          <t>57271</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92156</t>
+          <t>91398</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21943</t>
+          <t>22165</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47189</t>
+          <t>46224</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>129437</t>
+          <t>127842</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>290951</t>
+          <t>291701</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>326854</t>
+          <t>328218</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>216461</t>
+          <t>218373</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>243557</t>
+          <t>242855</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>517878</t>
+          <t>518680</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>563766</t>
+          <t>562974</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,24%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18282</t>
+          <t>17635</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>6727</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4227</t>
+          <t>4793</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21662</t>
+          <t>20668</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14681</t>
+          <t>13834</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>980</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8556</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18737</t>
+          <t>18511</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11074</t>
+          <t>10839</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5985,7 +5985,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10024</t>
+          <t>9364</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3057</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15203</t>
+          <t>15691</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48204</t>
+          <t>47692</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78306</t>
+          <t>77967</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13846</t>
+          <t>13516</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32641</t>
+          <t>32705</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>67108</t>
+          <t>65970</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>102669</t>
+          <t>100251</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>223436</t>
+          <t>222250</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>256973</t>
+          <t>256489</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>172996</t>
+          <t>172518</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>194583</t>
+          <t>194325</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>405647</t>
+          <t>405734</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>445216</t>
+          <t>445611</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,02%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5848</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22055</t>
+          <t>22567</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>6680</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23182</t>
+          <t>23099</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18208</t>
+          <t>21265</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>993</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12473</t>
+          <t>12206</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8014</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>25179</t>
+          <t>25423</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20129</t>
+          <t>18575</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>969</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>9683</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>6776</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23048</t>
+          <t>22887</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>73963</t>
+          <t>74935</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>107687</t>
+          <t>110491</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15360</t>
+          <t>14990</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36227</t>
+          <t>34847</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>94390</t>
+          <t>94750</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>133497</t>
+          <t>135234</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>273881</t>
+          <t>273566</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>313517</t>
+          <t>311794</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>254654</t>
+          <t>256714</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>278032</t>
+          <t>279312</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>540511</t>
+          <t>538138</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>585246</t>
+          <t>584106</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,43%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>19349</t>
+          <t>19021</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>43996</t>
+          <t>46400</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12073</t>
+          <t>10955</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>22776</t>
+          <t>22799</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>49848</t>
+          <t>49914</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>16346</t>
+          <t>14795</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>37129</t>
+          <t>36305</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>18501</t>
+          <t>19823</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>23643</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>48451</t>
+          <t>48675</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>27106</t>
+          <t>27716</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>53869</t>
+          <t>52386</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>20283</t>
+          <t>20018</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>37638</t>
+          <t>37422</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>67110</t>
+          <t>66128</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>230358</t>
+          <t>232813</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>290557</t>
+          <t>293484</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>72429</t>
+          <t>73280</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>113347</t>
+          <t>111801</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>315856</t>
+          <t>314963</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>386487</t>
+          <t>386864</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1027003</t>
+          <t>1026373</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1093307</t>
+          <t>1094718</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>808509</t>
+          <t>809864</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>850736</t>
+          <t>851963</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1855862</t>
+          <t>1852801</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1935645</t>
+          <t>1933838</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,82%</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>948</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7810</t>
+          <t>7754</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>6447</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10542</t>
+          <t>10605</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10470</t>
+          <t>11390</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>818</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7532</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>3682</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14388</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16554</t>
+          <t>16869</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34631</t>
+          <t>36441</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>16323</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23124</t>
+          <t>22780</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45135</t>
+          <t>45386</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>196156</t>
+          <t>196232</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>217291</t>
+          <t>217937</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>146147</t>
+          <t>146005</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>160259</t>
+          <t>160238</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>349349</t>
+          <t>350093</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>373948</t>
+          <t>375403</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,66%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15431</t>
+          <t>15444</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,47 +8714,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,76%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5315</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1804</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11350</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>0,66%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5315</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1842</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11866</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22350</t>
+          <t>22152</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10458</t>
+          <t>9766</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5588</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>889</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>11189</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>7449</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22200</t>
+          <t>23506</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9336</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26276</t>
+          <t>26152</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25840</t>
+          <t>27260</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50187</t>
+          <t>51989</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26254</t>
+          <t>26231</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41430</t>
+          <t>41751</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70890</t>
+          <t>71089</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>331891</t>
+          <t>332396</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>362809</t>
+          <t>362748</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>236218</t>
+          <t>237232</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>255719</t>
+          <t>256062</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>577530</t>
+          <t>576985</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>612027</t>
+          <t>613774</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,84%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6737</t>
+          <t>6732</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11372</t>
+          <t>11429</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13522</t>
+          <t>12745</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14390</t>
+          <t>14761</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3172</t>
+          <t>3111</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16445</t>
+          <t>15830</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>942</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>8703</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5974</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19920</t>
+          <t>18932</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44875</t>
+          <t>44829</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73725</t>
+          <t>74424</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16625</t>
+          <t>15602</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36484</t>
+          <t>36262</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>66600</t>
+          <t>66201</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>103890</t>
+          <t>103491</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>265356</t>
+          <t>265643</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>297571</t>
+          <t>297641</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>225778</t>
+          <t>227147</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>247555</t>
+          <t>248614</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>500232</t>
+          <t>498866</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>539578</t>
+          <t>540418</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,17%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2491</t>
+          <t>2493</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14244</t>
+          <t>12922</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12871</t>
+          <t>14427</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3652</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15690</t>
+          <t>16199</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5861</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4652</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>17661</t>
+          <t>17648</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10057</t>
+          <t>9871</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>26321</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4241</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17998</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>17113</t>
+          <t>16239</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>36785</t>
+          <t>38344</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>42546</t>
+          <t>41651</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>70705</t>
+          <t>69568</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14873</t>
+          <t>14908</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35475</t>
+          <t>34610</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>62608</t>
+          <t>63464</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>95905</t>
+          <t>97265</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>297280</t>
+          <t>295925</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>329193</t>
+          <t>329743</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>273010</t>
+          <t>272706</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>296519</t>
+          <t>295689</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>579521</t>
+          <t>576372</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>621395</t>
+          <t>618619</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>85,94%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>10160</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>28174</t>
+          <t>29471</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2846</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14310</t>
+          <t>15096</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>16509</t>
+          <t>17301</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>37130</t>
+          <t>37480</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10954</t>
+          <t>11203</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28978</t>
+          <t>31017</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>11999</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10913,7 +10913,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>16582</t>
+          <t>16179</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>37969</t>
+          <t>36764</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>30380</t>
+          <t>32406</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>58455</t>
+          <t>58926</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9850</t>
+          <t>10351</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>27766</t>
+          <t>26744</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>45425</t>
+          <t>47192</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>79346</t>
+          <t>81257</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>151607</t>
+          <t>152009</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>205467</t>
+          <t>202274</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>57211</t>
+          <t>58627</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>93539</t>
+          <t>93620</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>221237</t>
+          <t>220117</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>283914</t>
+          <t>283093</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1117800</t>
+          <t>1120526</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1179155</t>
+          <t>1180135</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>903536</t>
+          <t>905136</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>944572</t>
+          <t>945178</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2039275</t>
+          <t>2037468</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2111529</t>
+          <t>2111757</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,56%</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2181</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7478</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11724,7 +11724,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2181</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -11767,22 +11767,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3539</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t>9978</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11802,32 +11802,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>576</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>5775</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11837,32 +11837,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10092</t>
+          <t>12049</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -11880,32 +11880,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9430</t>
+          <t>11767</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3688</t>
+          <t>5453</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22990</t>
+          <t>24806</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11915,32 +11915,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3548</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>7800</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11950,32 +11950,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>12978</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>8690</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>30386</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -11993,32 +11993,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36143</t>
+          <t>40183</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>26557</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52071</t>
+          <t>55158</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12028,32 +12028,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12329</t>
+          <t>13151</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8321</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17841</t>
+          <t>19226</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12063,32 +12063,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>48472</t>
+          <t>53334</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36822</t>
+          <t>39605</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64271</t>
+          <t>71641</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -12106,32 +12106,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>281684</t>
+          <t>308843</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>262650</t>
+          <t>290620</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>294991</t>
+          <t>324411</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12141,32 +12141,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>240592</t>
+          <t>260486</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>233759</t>
+          <t>253789</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>245847</t>
+          <t>266430</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12176,32 +12176,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>522276</t>
+          <t>569329</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>503966</t>
+          <t>550282</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>536859</t>
+          <t>586476</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,78%</t>
         </is>
       </c>
     </row>
@@ -12219,17 +12219,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>332977</t>
+          <t>366814</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>332977</t>
+          <t>366814</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>332977</t>
+          <t>366814</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12254,17 +12254,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>257846</t>
+          <t>279222</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>257846</t>
+          <t>279222</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>257846</t>
+          <t>279222</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12289,17 +12289,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>590823</t>
+          <t>646035</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>590823</t>
+          <t>646035</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>590823</t>
+          <t>646035</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12336,32 +12336,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14283</t>
+          <t>15394</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>8169</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25959</t>
+          <t>25219</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12371,32 +12371,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7387</t>
+          <t>8146</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12406,32 +12406,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>17239</t>
+          <t>18994</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>11233</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27837</t>
+          <t>30525</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -12449,32 +12449,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>256973</t>
+          <t>13892</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13409</t>
+          <t>7529</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>539719</t>
+          <t>24094</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12484,32 +12484,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7055</t>
+          <t>7580</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3693</t>
+          <t>3828</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13367</t>
+          <t>14678</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12519,32 +12519,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>264029</t>
+          <t>21471</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20594</t>
+          <t>13988</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>724394</t>
+          <t>32009</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -12562,32 +12562,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27892</t>
+          <t>29712</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11663</t>
+          <t>18438</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46840</t>
+          <t>42901</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12597,32 +12597,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>5792</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9672</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12632,32 +12632,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>32668</t>
+          <t>35505</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15681</t>
+          <t>23645</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>50639</t>
+          <t>49114</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -12675,32 +12675,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>53213</t>
+          <t>61820</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21126</t>
+          <t>46521</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82701</t>
+          <t>78002</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12710,32 +12710,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30797</t>
+          <t>33879</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22967</t>
+          <t>25111</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40622</t>
+          <t>44804</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12745,32 +12745,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>84009</t>
+          <t>95699</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41928</t>
+          <t>78354</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>112276</t>
+          <t>115080</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -12788,32 +12788,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>450906</t>
+          <t>503281</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>212818</t>
+          <t>480155</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>657186</t>
+          <t>523328</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12823,32 +12823,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>356800</t>
+          <t>399285</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>345829</t>
+          <t>384741</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>367125</t>
+          <t>409545</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12858,32 +12858,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>807706</t>
+          <t>902566</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>407914</t>
+          <t>877721</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1019210</t>
+          <t>926359</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>86,23%</t>
         </is>
       </c>
     </row>
@@ -12901,17 +12901,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>803267</t>
+          <t>624099</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>803267</t>
+          <t>624099</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>803267</t>
+          <t>624099</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12936,17 +12936,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>402384</t>
+          <t>450136</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>402384</t>
+          <t>450136</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>402384</t>
+          <t>450136</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12971,17 +12971,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1205651</t>
+          <t>1074235</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1205651</t>
+          <t>1074235</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1205651</t>
+          <t>1074235</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13018,32 +13018,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11851</t>
+          <t>11776</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6036</t>
+          <t>5611</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22085</t>
+          <t>21543</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1431</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -13063,12 +13063,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>4992</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -13078,7 +13078,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13088,32 +13088,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>13254</t>
+          <t>13207</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24181</t>
+          <t>24722</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -13131,32 +13131,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7992</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>3087</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17130</t>
+          <t>16503</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13166,32 +13166,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>8445</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13201,32 +13201,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>11036</t>
+          <t>11399</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19868</t>
+          <t>18987</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -13244,32 +13244,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11846</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>6807</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20647</t>
+          <t>21204</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13279,67 +13279,67 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>4674</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1719</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9673</t>
+          <t>10425</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>3,11%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>16869</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>10630</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>26562</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>1,42%</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>16408</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>9558</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>26639</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -13357,32 +13357,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>41909</t>
+          <t>46732</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30004</t>
+          <t>34051</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55782</t>
+          <t>61940</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13392,32 +13392,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17508</t>
+          <t>21367</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10314</t>
+          <t>14926</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24922</t>
+          <t>30456</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13427,27 +13427,27 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>59417</t>
+          <t>68100</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45281</t>
+          <t>52366</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>76528</t>
+          <t>85100</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -13470,32 +13470,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>278338</t>
+          <t>334724</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261356</t>
+          <t>314115</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>294825</t>
+          <t>350767</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13505,32 +13505,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>293750</t>
+          <t>303609</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>284477</t>
+          <t>293000</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>302961</t>
+          <t>311767</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13540,32 +13540,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>572089</t>
+          <t>638333</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>549840</t>
+          <t>617200</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>592354</t>
+          <t>657352</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>87,89%</t>
         </is>
       </c>
     </row>
@@ -13583,17 +13583,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>351935</t>
+          <t>413045</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>351935</t>
+          <t>413045</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>351935</t>
+          <t>413045</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13618,17 +13618,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>320269</t>
+          <t>334862</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>320269</t>
+          <t>334862</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>320269</t>
+          <t>334862</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>672205</t>
+          <t>747907</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>672205</t>
+          <t>747907</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>672205</t>
+          <t>747907</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13700,32 +13700,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>11958</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6243</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20510</t>
+          <t>20294</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13735,32 +13735,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9265</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13770,32 +13770,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>16165</t>
+          <t>16933</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9560</t>
+          <t>10689</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25592</t>
+          <t>26397</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -13813,32 +13813,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11610</t>
+          <t>11352</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13848,32 +13848,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9076</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13883,32 +13883,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>10139</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>5874</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>17510</t>
+          <t>17324</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -13926,32 +13926,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9468</t>
+          <t>9581</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16686</t>
+          <t>16059</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13961,32 +13961,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7045</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3399</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13195</t>
+          <t>12627</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13996,32 +13996,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>16513</t>
+          <t>16949</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>10867</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24945</t>
+          <t>24862</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -14039,32 +14039,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>45957</t>
+          <t>47771</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34234</t>
+          <t>35683</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>60804</t>
+          <t>63801</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14074,32 +14074,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>27941</t>
+          <t>30465</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>22017</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39644</t>
+          <t>40692</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14109,32 +14109,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>73898</t>
+          <t>78236</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>55448</t>
+          <t>63684</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>93440</t>
+          <t>97111</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -14152,32 +14152,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>395742</t>
+          <t>439211</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>379996</t>
+          <t>422434</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>410094</t>
+          <t>454923</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14187,32 +14187,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>437150</t>
+          <t>399971</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>423379</t>
+          <t>388549</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>453866</t>
+          <t>410633</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14222,32 +14222,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>832893</t>
+          <t>839181</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>810918</t>
+          <t>817597</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>860414</t>
+          <t>856092</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>89,02%</t>
         </is>
       </c>
     </row>
@@ -14265,17 +14265,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>468451</t>
+          <t>514114</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>468451</t>
+          <t>514114</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>468451</t>
+          <t>514114</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14300,17 +14300,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>481156</t>
+          <t>447545</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>481156</t>
+          <t>447545</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>481156</t>
+          <t>447545</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>949608</t>
+          <t>961658</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>949608</t>
+          <t>961658</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>949608</t>
+          <t>961658</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14382,32 +14382,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>40076</t>
+          <t>41391</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>26135</t>
+          <t>28161</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>56873</t>
+          <t>55314</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14417,32 +14417,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>10007</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4662</t>
+          <t>5748</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15454</t>
+          <t>17084</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14452,32 +14452,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>48839</t>
+          <t>51398</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>34726</t>
+          <t>38450</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>65618</t>
+          <t>66520</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -14495,32 +14495,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>274027</t>
+          <t>30860</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29133</t>
+          <t>21104</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>841803</t>
+          <t>43360</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14530,32 +14530,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>16093</t>
+          <t>18241</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>11874</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>24807</t>
+          <t>25957</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14565,32 +14565,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>290120</t>
+          <t>49101</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>44420</t>
+          <t>36803</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1046500</t>
+          <t>64714</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -14608,102 +14608,102 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>58635</t>
+          <t>63255</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>37895</t>
+          <t>47337</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>81067</t>
+          <t>83093</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>21303</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>14574</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>30528</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>84558</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>66385</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>108738</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
           <t>1,94%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>19932</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>13638</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>28578</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>78567</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>56775</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>99179</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -14721,32 +14721,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>177222</t>
+          <t>196506</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>115859</t>
+          <t>168742</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>215602</t>
+          <t>228032</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14756,32 +14756,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>88575</t>
+          <t>98863</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>71042</t>
+          <t>82335</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>104656</t>
+          <t>115547</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14791,32 +14791,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>265797</t>
+          <t>295369</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>210249</t>
+          <t>264418</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>310194</t>
+          <t>331886</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -14834,32 +14834,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1406670</t>
+          <t>1586058</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>923314</t>
+          <t>1549959</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1620453</t>
+          <t>1624437</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14869,32 +14869,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1328293</t>
+          <t>1363351</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1307397</t>
+          <t>1342452</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1351317</t>
+          <t>1381816</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14904,32 +14904,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>2734963</t>
+          <t>2949409</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2062109</t>
+          <t>2908013</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2959472</t>
+          <t>2991043</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>87,21%</t>
         </is>
       </c>
     </row>
@@ -14947,17 +14947,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1956631</t>
+          <t>1918071</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1956631</t>
+          <t>1918071</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1956631</t>
+          <t>1918071</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14982,17 +14982,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1461656</t>
+          <t>1511765</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1461656</t>
+          <t>1511765</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1461656</t>
+          <t>1511765</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15017,17 +15017,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>3418287</t>
+          <t>3429836</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3418287</t>
+          <t>3429836</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3418287</t>
+          <t>3429836</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
